--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -67,24 +67,24 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cake</x:t>
+  </x:si>
+  <x:si>
     <x:t>Pivot table that is using a connection to another workbook as a source of pivot cache. Connection uses absolute path, so it is necessary to update the path (Pivot Table Analyze - Change Data Source - Connection Properties - Definition).</x:t>
   </x:si>
   <x:si>
+    <x:t>Pivot table that uses area in 'Area Source' sheet as a source of data for the pivot cache.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Pivot table that uses external workbook reference as a source of data for the pivot cache.</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pivot table that uses area in 'Area Source' sheet as a source of data for the pivot cache.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Pivot table that uses a table named 'Table1' as a source of data for the pivot cache.</x:t>
   </x:si>
   <x:si>
@@ -97,43 +97,43 @@
     <x:t>Total with tax</x:t>
   </x:si>
   <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$B$5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Expensive</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Original</x:t>
+  </x:si>
+  <x:si>
     <x:t>$B$2:$B$3 by</x:t>
   </x:si>
   <x:si>
     <x:t>(All)</x:t>
   </x:si>
   <x:si>
-    <x:t>Row Labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$B$5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Expensive</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Original</x:t>
+    <x:t>Muffin</x:t>
   </x:si>
   <x:si>
     <x:t>Tax</x:t>
   </x:si>
   <x:si>
-    <x:t>Muffin</x:t>
+    <x:t>Sum of Value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Column Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
   </x:si>
   <x:si>
     <x:t>Page1</x:t>
   </x:si>
   <x:si>
     <x:t>Page2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum of Value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Column Labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grand Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1159,7 +1159,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1275,23 +1275,23 @@
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <x:c r="A4" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>151.25</x:v>
@@ -1299,7 +1299,7 @@
     </x:row>
     <x:row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <x:c r="A5" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>30.25</x:v>
@@ -1324,27 +1324,27 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>1.21</x:v>
@@ -1352,7 +1352,7 @@
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>17</x:v>
@@ -1383,45 +1383,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>1.21</x:v>
@@ -1435,7 +1435,7 @@
     </x:row>
     <x:row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A7" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>17</x:v>
@@ -1446,7 +1446,7 @@
     </x:row>
     <x:row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <x:c r="A8" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0">
         <x:v>1.21</x:v>
@@ -1477,7 +1477,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1589,15 +1589,15 @@
   <x:sheetData>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="D3" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <x:c r="D4" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>1</x:v>
@@ -1622,7 +1622,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="A1" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1734,15 +1734,15 @@
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="B2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>1</x:v>
@@ -1881,15 +1881,15 @@
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="B2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>1</x:v>
@@ -2026,7 +2026,7 @@
   <x:sheetData>
     <x:row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <x:c r="A2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>10</x:v>

--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -1151,14 +1151,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{5DF7487B-601B-4CF1-83DA-637CE4ACBFAA}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1253,39 +1250,32 @@
       <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{ECC5C1F4-162A-4495-BD7F-5FACEE21B0F8}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B5"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.554688" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="7" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="12.554688" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -1293,7 +1283,7 @@
       <x:c r="A4" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>151.25</x:v>
       </x:c>
     </x:row>
@@ -1301,121 +1291,107 @@
       <x:c r="A5" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>30.25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{A9F178DE-BBB7-489C-9228-24C8800DF773}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E3"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E1" s="0" t="s">
+      <x:c r="E1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>1.21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{4A4D42AF-FE37-4EC3-9D02-CE3B6F12778F}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D8"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.554688" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="15.554688" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="5.777344" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="10.777344" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="12.554688" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="15.554688" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="5.777344" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="10.777344" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="A4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="A5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1423,13 +1399,13 @@
       <x:c r="A6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>1.21</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>26.21</x:v>
       </x:c>
     </x:row>
@@ -1437,10 +1413,10 @@
       <x:c r="A7" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C7" s="0">
+      <x:c r="C7">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -1448,35 +1424,28 @@
       <x:c r="A8" s="11" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B8" s="0">
+      <x:c r="B8">
         <x:v>1.21</x:v>
       </x:c>
-      <x:c r="C8" s="0">
+      <x:c r="C8">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D8" s="0">
+      <x:c r="D8">
         <x:v>43.21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{157D16F0-CB70-40FE-8801-5E78DDAC6F12}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1571,57 +1540,43 @@
       <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{7B95AC8F-0A2B-4305-8907-61BCB849A9DA}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="D3:E4"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{BF5682F4-C374-4D89-9ECF-B07973C4759C}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1716,43 +1671,33 @@
       <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{A96ED509-A698-481D-9229-D61A1CAE8227}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B2:C3"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId1"/>
   </x:tableParts>
@@ -1761,14 +1706,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{076680DD-97CF-4D98-B4D1-7E5361715DFA}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -1863,57 +1805,43 @@
       <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{388DAB8D-43FF-4D7B-9586-E2AB978B4CFD}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="B2:C3"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C3" s="0">
+      <x:c r="C3">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{93B5D2A0-EF2B-4557-801E-486063C03CDD}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C20"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -2008,43 +1936,36 @@
       <x:c r="C20" s="9"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{EBB5288C-1114-45E0-9330-28F95507E82B}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A2:B5"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:sheetData>
     <x:row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B2" s="0">
+      <x:c r="B2">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="0">
+      <x:c r="B3">
         <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <x:c r="A5" s="0" t="s">
+      <x:c r="A5" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:f>(B2+B3)*1.21</x:f>
         <x:v>30.25</x:v>
       </x:c>
@@ -2060,10 +1981,6 @@
       <x:inputCells r="B3" val="75"/>
     </x:scenario>
   </x:scenarios>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Sources/PivotTable-AllSources-output.xlsx
@@ -1259,7 +1259,7 @@
   <x:dimension ref="A1:B5"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.554688" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1351,10 +1351,10 @@
   <x:dimension ref="A1:D8"/>
   <x:sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.554688" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="15.554688" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="5.777344" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="10.777344" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" x14ac:dyDescent="0.3">
